--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -27223,7 +27223,7 @@
         <v>21125</v>
       </c>
       <c r="K64" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65">
@@ -30808,7 +30808,7 @@
         <v>3385</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3817,7 +3817,7 @@
         <v>12296</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -20040,7 +20040,7 @@
         <v>236</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -23625,7 +23625,7 @@
         <v>5671</v>
       </c>
       <c r="K64" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -45037,7 +45037,7 @@
         <v>317</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -51504,7 +51504,7 @@
         <v>7510</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -3814,10 +3814,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J64" t="n">
-        <v>12296</v>
+        <v>12318</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>110578</v>
@@ -27220,10 +27220,10 @@
         <v>0.006838967641551252</v>
       </c>
       <c r="J64" t="n">
-        <v>21125</v>
+        <v>21145</v>
       </c>
       <c r="K64" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -41452,7 +41452,7 @@
         <v>3141</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.005369127516778523</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -13829,10 +13829,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -20037,10 +20037,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>110578</v>
@@ -27220,10 +27220,10 @@
         <v>0.006838967641551252</v>
       </c>
       <c r="J64" t="n">
-        <v>21145</v>
+        <v>21179</v>
       </c>
       <c r="K64" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -30805,10 +30805,10 @@
         <v>0.4724201333026891</v>
       </c>
       <c r="J64" t="n">
-        <v>3385</v>
+        <v>3393</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37901,10 +37901,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -41449,10 +41449,10 @@
         <v>0.00147918574346693</v>
       </c>
       <c r="J63" t="n">
-        <v>3141</v>
+        <v>3150</v>
       </c>
       <c r="K63" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -45034,10 +45034,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>
@@ -51501,10 +51501,10 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J64" t="n">
-        <v>7510</v>
+        <v>7518</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22470</v>
+        <v>22782</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.005369127516778523</v>
+        <v>0.01932885906040268</v>
       </c>
       <c r="E64" t="n">
         <v>13</v>
@@ -10300,7 +10300,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.2240320427236315</v>
+        <v>-0.2346589412694232</v>
       </c>
       <c r="E65" t="n">
         <v>16</v>
@@ -23622,10 +23622,10 @@
         <v>0.1792611820312651</v>
       </c>
       <c r="J64" t="n">
-        <v>5671</v>
+        <v>5687</v>
       </c>
       <c r="K64" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
@@ -41449,10 +41449,10 @@
         <v>0.00147918574346693</v>
       </c>
       <c r="J63" t="n">
-        <v>3150</v>
+        <v>3152</v>
       </c>
       <c r="K63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -3814,10 +3814,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J64" t="n">
-        <v>12318</v>
+        <v>12323</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -23622,10 +23622,10 @@
         <v>0.1792611820312651</v>
       </c>
       <c r="J64" t="n">
-        <v>5687</v>
+        <v>5695</v>
       </c>
       <c r="K64" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>110578</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.01566063959249087</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>63824</v>
@@ -6829,7 +6829,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -10266,7 +10266,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20022,7 +20022,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -23607,7 +23607,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>36795</v>
@@ -27205,7 +27205,7 @@
         <v>0.008422542550171679</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>110578</v>
@@ -30790,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>38360</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -37886,7 +37886,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41434,7 +41434,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>56757</v>
@@ -45019,7 +45019,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -48049,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -51486,7 +51486,7 @@
         <v>0.002546845829395902</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -23625,7 +23625,7 @@
         <v>5695</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -3814,7 +3814,7 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J64" t="n">
-        <v>12323</v>
+        <v>12324</v>
       </c>
       <c r="K64" t="n">
         <v>4</v>
@@ -23622,7 +23622,7 @@
         <v>0.1792611820312651</v>
       </c>
       <c r="J64" t="n">
-        <v>5695</v>
+        <v>5693</v>
       </c>
       <c r="K64" t="n">
         <v>14</v>
@@ -27220,7 +27220,7 @@
         <v>0.006838967641551252</v>
       </c>
       <c r="J64" t="n">
-        <v>21179</v>
+        <v>21181</v>
       </c>
       <c r="K64" t="n">
         <v>9</v>
@@ -51501,7 +51501,7 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J64" t="n">
-        <v>7518</v>
+        <v>7517</v>
       </c>
       <c r="K64" t="n">
         <v>5</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -27815,7 +27815,7 @@
         <v>21181</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21181</v>
+        <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74">
@@ -31437,7 +31437,7 @@
         <v>3393</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -10691,7 +10691,7 @@
         <v>762</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -10691,7 +10691,7 @@
         <v>762</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -42192,7 +42192,7 @@
         <v>3152</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21174</v>
       </c>
       <c r="K73" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74">
@@ -31437,7 +31437,7 @@
         <v>3393</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -42192,7 +42192,7 @@
         <v>3152</v>
       </c>
       <c r="K72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12324</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
@@ -35022,7 +35022,7 @@
         <v>349</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -42192,7 +42192,7 @@
         <v>3152</v>
       </c>
       <c r="K72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21174</v>
+        <v>21170</v>
       </c>
       <c r="K73" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4147,10 +4147,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J73" t="n">
-        <v>12324</v>
+        <v>12338</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -10688,10 +10688,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="K73" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -24180,7 +24180,7 @@
         <v>5693</v>
       </c>
       <c r="K73" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74">
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21170</v>
+        <v>21241</v>
       </c>
       <c r="K73" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -42192,7 +42192,7 @@
         <v>3152</v>
       </c>
       <c r="K72" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -52355,7 +52355,7 @@
         <v>7517</v>
       </c>
       <c r="K73" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4147,10 +4147,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J73" t="n">
-        <v>12338</v>
+        <v>12349</v>
       </c>
       <c r="K73" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -31434,10 +31434,10 @@
         <v>0.003262515007569035</v>
       </c>
       <c r="J73" t="n">
-        <v>3393</v>
+        <v>3398</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -42189,10 +42189,10 @@
         <v>0.00147918574346693</v>
       </c>
       <c r="J72" t="n">
-        <v>3152</v>
+        <v>3161</v>
       </c>
       <c r="K72" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -45814,7 +45814,7 @@
         <v>318</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -52352,10 +52352,10 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J73" t="n">
-        <v>7517</v>
+        <v>7546</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4150,7 +4150,7 @@
         <v>12349</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -24177,10 +24177,10 @@
         <v>0.1833184309761692</v>
       </c>
       <c r="J73" t="n">
-        <v>5693</v>
+        <v>5742</v>
       </c>
       <c r="K73" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -27815,7 +27815,7 @@
         <v>21241</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -35019,10 +35019,10 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -42192,7 +42192,7 @@
         <v>3161</v>
       </c>
       <c r="K72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -45811,10 +45811,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21241</v>
+        <v>21219</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -2541,7 +2541,7 @@
         <v>0.01425992270585912</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>40886</v>
@@ -4147,10 +4147,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J73" t="n">
-        <v>12349</v>
+        <v>12354</v>
       </c>
       <c r="K73" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -5904,7 +5904,7 @@
         <v>-0.4882323485227842</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -9082,7 +9082,7 @@
         <v>0.1825533379215416</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -10688,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="K73" t="n">
         <v>16</v>
@@ -12667,7 +12667,7 @@
         <v>-0.5361966236345581</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -16030,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
         <v>0.0186880956830499</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>18875</v>
@@ -22571,7 +22571,7 @@
         <v>0.03767525535616052</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>33267</v>
@@ -26206,7 +26206,7 @@
         <v>0.00289162432980582</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>71324</v>
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21219</v>
+        <v>21232</v>
       </c>
       <c r="K73" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -29828,7 +29828,7 @@
         <v>0.05226338383264815</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>18875</v>
@@ -33413,7 +33413,7 @@
         <v>0.09378305323774827</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -36998,7 +36998,7 @@
         <v>0.03606497201064513</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -40583,7 +40583,7 @@
         <v>0.0118006509177054</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>56747</v>
@@ -44205,7 +44205,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -47568,7 +47568,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -50746,7 +50746,7 @@
         <v>0.02457378877572281</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>43203</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4132,7 +4132,7 @@
         <v>0.01386049228645017</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>63824</v>
@@ -7162,7 +7162,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -10688,10 +10688,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -14258,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -24162,7 +24162,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>36795</v>
@@ -24177,7 +24177,7 @@
         <v>0.1833184309761692</v>
       </c>
       <c r="J73" t="n">
-        <v>5742</v>
+        <v>5735</v>
       </c>
       <c r="K73" t="n">
         <v>10</v>
@@ -27797,7 +27797,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>110578</v>
@@ -27812,10 +27812,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J73" t="n">
-        <v>21232</v>
+        <v>21235</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -31419,7 +31419,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>38360</v>
@@ -31434,7 +31434,7 @@
         <v>0.003262515007569035</v>
       </c>
       <c r="J73" t="n">
-        <v>3398</v>
+        <v>3395</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -35004,7 +35004,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -38589,7 +38589,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -42174,7 +42174,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>56757</v>
@@ -42189,10 +42189,10 @@
         <v>0.00147918574346693</v>
       </c>
       <c r="J72" t="n">
-        <v>3161</v>
+        <v>3156</v>
       </c>
       <c r="K72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -48826,7 +48826,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -52337,7 +52337,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>52385</v>
@@ -52352,10 +52352,10 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J73" t="n">
-        <v>7546</v>
+        <v>7535</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -42923,10 +42923,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.00147918574346693</v>
+        <v>0.002430090864267099</v>
       </c>
       <c r="J81" t="n">
         <v>3156</v>

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -11095,10 +11095,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -28407,7 +28407,7 @@
         <v>21237</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -28407,7 +28407,7 @@
         <v>21237</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
@@ -28407,7 +28407,7 @@
         <v>21237</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -28407,7 +28407,7 @@
         <v>21237</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -28407,7 +28407,7 @@
         <v>21237</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21237</v>
+        <v>21234</v>
       </c>
       <c r="K82" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83">
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01394126082107388</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>63824</v>
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -7495,7 +7495,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14702,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -21058,7 +21058,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>36795</v>
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -28389,7 +28389,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>110578</v>
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21234</v>
+        <v>21235</v>
       </c>
       <c r="K82" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
@@ -32048,7 +32048,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>38360</v>
@@ -35670,7 +35670,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -39292,7 +39292,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -39310,7 +39310,7 @@
         <v>530</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -42914,7 +42914,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>56757</v>
@@ -46573,7 +46573,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -49603,7 +49603,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -53188,7 +53188,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>52385</v>
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -32066,7 +32066,7 @@
         <v>3395</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -11098,7 +11098,7 @@
         <v>762</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21235</v>
+        <v>21234</v>
       </c>
       <c r="K82" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01394126082107388</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>63824</v>
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -7495,7 +7495,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14702,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -21058,7 +21058,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>36795</v>
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
@@ -28389,7 +28389,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>110578</v>
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21234</v>
+        <v>21248</v>
       </c>
       <c r="K82" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -32048,7 +32048,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>38360</v>
@@ -32066,7 +32066,7 @@
         <v>3395</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -35670,7 +35670,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -39292,7 +39292,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -42914,7 +42914,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>56757</v>
@@ -42932,7 +42932,7 @@
         <v>3156</v>
       </c>
       <c r="K81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
@@ -46573,7 +46573,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -49603,7 +49603,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -53188,7 +53188,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>52385</v>
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01394126082107388</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>63824</v>
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -7495,7 +7495,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14702,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -21058,7 +21058,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>36795</v>
@@ -24735,7 +24735,7 @@
         <v>5737</v>
       </c>
       <c r="K82" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
@@ -28389,7 +28389,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>110578</v>
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21248</v>
+        <v>21276</v>
       </c>
       <c r="K82" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -32048,7 +32048,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>38360</v>
@@ -35670,7 +35670,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -39292,7 +39292,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -42914,7 +42914,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>56757</v>
@@ -42932,7 +42932,7 @@
         <v>3156</v>
       </c>
       <c r="K81" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
@@ -46573,7 +46573,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -49603,7 +49603,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -53188,7 +53188,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>52385</v>
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4465,7 +4465,7 @@
         <v>0.01394126082107388</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>63824</v>
@@ -4483,7 +4483,7 @@
         <v>12354</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -7495,7 +7495,7 @@
         <v>-0.318294701986755</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0.01932885906040268</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -14702,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -21058,7 +21058,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>36795</v>
@@ -28389,7 +28389,7 @@
         <v>0.003983678146679881</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>110578</v>
@@ -28407,7 +28407,7 @@
         <v>21276</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -32048,7 +32048,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>38360</v>
@@ -32066,7 +32066,7 @@
         <v>3395</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -35670,7 +35670,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -39292,7 +39292,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -42914,7 +42914,7 @@
         <v>0.0053720448627258</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
         <v>56757</v>
@@ -42932,7 +42932,7 @@
         <v>3156</v>
       </c>
       <c r="K81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -46573,7 +46573,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -49603,7 +49603,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -53188,7 +53188,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>52385</v>
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21276</v>
+        <v>21273</v>
       </c>
       <c r="K82" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4480,10 +4480,10 @@
         <v>0.02998311453215084</v>
       </c>
       <c r="J82" t="n">
-        <v>12354</v>
+        <v>12382</v>
       </c>
       <c r="K82" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -21076,7 +21076,7 @@
         <v>237</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -24732,10 +24732,10 @@
         <v>0.1833184309761692</v>
       </c>
       <c r="J82" t="n">
-        <v>5737</v>
+        <v>5757</v>
       </c>
       <c r="K82" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -28407,7 +28407,7 @@
         <v>21273</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -32063,10 +32063,10 @@
         <v>0.003262515007569035</v>
       </c>
       <c r="J82" t="n">
-        <v>3395</v>
+        <v>3400</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -39307,10 +39307,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -42929,10 +42929,10 @@
         <v>0.002430090864267099</v>
       </c>
       <c r="J81" t="n">
-        <v>3156</v>
+        <v>3174</v>
       </c>
       <c r="K81" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -53206,7 +53206,7 @@
         <v>7533</v>
       </c>
       <c r="K82" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -4483,7 +4483,7 @@
         <v>12382</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -28407,7 +28407,7 @@
         <v>21273</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -42932,7 +42932,7 @@
         <v>3174</v>
       </c>
       <c r="K81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -11095,10 +11095,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -21073,10 +21073,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -24732,10 +24732,10 @@
         <v>0.1833184309761692</v>
       </c>
       <c r="J82" t="n">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -28404,10 +28404,10 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21273</v>
+        <v>21287</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -53203,10 +53203,10 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J82" t="n">
-        <v>7533</v>
+        <v>7558</v>
       </c>
       <c r="K82" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroAUA.xlsx
+++ b/regionais/registroAUA.xlsx
@@ -28404,7 +28404,7 @@
         <v>0.003525444512568976</v>
       </c>
       <c r="J82" t="n">
-        <v>21287</v>
+        <v>21284</v>
       </c>
       <c r="K82" t="n">
         <v>3</v>
@@ -53203,7 +53203,7 @@
         <v>0.2125315371617712</v>
       </c>
       <c r="J82" t="n">
-        <v>7558</v>
+        <v>7560</v>
       </c>
       <c r="K82" t="n">
         <v>3</v>
